--- a/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0002T0006Z000C1N55_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0002T0006Z000C1N55_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>50.37559790843998</v>
+        <v>8.186034660121496</v>
       </c>
       <c r="D2" t="n">
-        <v>45.13050927346029</v>
+        <v>7.333707756937297</v>
       </c>
       <c r="E2" t="n">
-        <v>5.947504451308563</v>
+        <v>0.9664694733376413</v>
       </c>
       <c r="F2" t="n">
-        <v>13.34339047207737</v>
+        <v>2.168300951712572</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>54.90446247801722</v>
+        <v>8.921975152677797</v>
       </c>
       <c r="D3" t="n">
-        <v>76.75783711374424</v>
+        <v>12.47314853098344</v>
       </c>
       <c r="E3" t="n">
-        <v>5.947504451308563</v>
+        <v>0.9664694733376413</v>
       </c>
       <c r="F3" t="n">
-        <v>13.34339047207737</v>
+        <v>2.168300951712572</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>51.18444322319512</v>
+        <v>8.317472023769207</v>
       </c>
       <c r="D4" t="n">
-        <v>51.32297948508744</v>
+        <v>8.339984166326708</v>
       </c>
       <c r="E4" t="n">
-        <v>5.947504451308563</v>
+        <v>0.9664694733376413</v>
       </c>
       <c r="F4" t="n">
-        <v>13.34339047207737</v>
+        <v>2.168300951712572</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>65.31150284312953</v>
+        <v>10.61311921200855</v>
       </c>
       <c r="D5" t="n">
-        <v>71.89473389978328</v>
+        <v>11.68289425871478</v>
       </c>
       <c r="E5" t="n">
-        <v>5.947504451308563</v>
+        <v>0.9664694733376413</v>
       </c>
       <c r="F5" t="n">
-        <v>13.34339047207737</v>
+        <v>2.168300951712572</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
